--- a/backend/data/financials_by_company/0385.HK.xlsx
+++ b/backend/data/financials_by_company/0385.HK.xlsx
@@ -4315,7 +4315,7 @@
         <v>-2991000</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>-0.048</v>
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
         <v>-0.0519</v>
